--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Sanzioni amministrative.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Sanzioni amministrative.xlsx
@@ -356,7 +356,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
